--- a/web/public/forms/gongnaeyeok-hanbeol.xlsx
+++ b/web/public/forms/gongnaeyeok-hanbeol.xlsx
@@ -755,7 +755,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>※ 양식 제공 : K-건설맵  k-conmap.com  —  공공 입찰 투찰금액 계산 · 개찰 결과 무료</t>
+          <t>※ 양식 제공 : K-건설맵  k-conmap.com  —  공공 입찰 투찰금액 계산 · 개찰 결과</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7465,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -19589,7 +19589,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>
@@ -20574,7 +20574,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
     </row>

--- a/web/public/forms/gongnaeyeok-hanbeol.xlsx
+++ b/web/public/forms/gongnaeyeok-hanbeol.xlsx
@@ -755,7 +755,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>※ 양식 제공 : K-건설맵  k-conmap.com  —  공공 입찰 투찰금액 계산 · 개찰 결과</t>
+          <t>※ 양식 제공 : K-건설맵  k-conmap.com  —  공공 입찰 투찰금액 계산 · 개찰 결과 무료</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7465,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -19589,7 +19589,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
@@ -20574,7 +20574,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
     </row>
